--- a/Bike-Repair-Source-Workbooks/Bike-Repair-Module-3-3.xlsx
+++ b/Bike-Repair-Source-Workbooks/Bike-Repair-Module-3-3.xlsx
@@ -88,7 +88,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -116,11 +116,12 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -155,6 +156,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2019,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H67"/>
+  <dimension ref="B1:D67"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2090,7 +2093,7 @@
           <t>Fixtures — Company received at formation (June 1)</t>
         </is>
       </c>
-      <c r="C7" s="17" t="n"/>
+      <c r="C7" s="25" t="n"/>
       <c r="D7" s="4" t="n">
         <v>750</v>
       </c>
@@ -2101,7 +2104,7 @@
           <t>Laptop — Company received at formation (June 1)</t>
         </is>
       </c>
-      <c r="C8" s="17" t="n"/>
+      <c r="C8" s="25" t="n"/>
       <c r="D8" s="4" t="n">
         <v>610</v>
       </c>
@@ -2223,7 +2226,7 @@
           <t>Parts used — Priya S.</t>
         </is>
       </c>
-      <c r="C20" s="17" t="n"/>
+      <c r="C20" s="25" t="n"/>
       <c r="D20" s="4" t="n">
         <v>-25</v>
       </c>

--- a/Bike-Repair-Source-Workbooks/Bike-Repair-Module-3-3.xlsx
+++ b/Bike-Repair-Source-Workbooks/Bike-Repair-Module-3-3.xlsx
@@ -2087,7 +2087,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="7" collapsed="1">
+    <row r="7" hidden="1" outlineLevel="1">
       <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Fixtures — Company received at formation (June 1)</t>
@@ -2098,7 +2098,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="1" outlineLevel="1">
       <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Laptop — Company received at formation (June 1)</t>
@@ -2109,7 +2109,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="1" outlineLevel="1">
       <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Credit Card — Company assumed the claim at formation (June 1)</t>
@@ -2119,7 +2119,7 @@
         <v>-2030</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="1" outlineLevel="1">
       <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Customer Deposit — Company assumed the claim at formation (June 1)</t>
@@ -2130,7 +2130,7 @@
         <v>-220</v>
       </c>
     </row>
-    <row r="11" hidden="1" outlineLevel="1">
+    <row r="11" collapsed="1">
       <c r="B11" s="16" t="inlineStr">
         <is>
           <t>Balance, June 1, 2026</t>
@@ -2143,7 +2143,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" hidden="1" outlineLevel="1">
+    <row r="12">
       <c r="B12" s="16" t="inlineStr">
         <is>
           <t>Balance, August 31, 2026</t>
@@ -2156,11 +2156,11 @@
         <v/>
       </c>
     </row>
-    <row r="13" hidden="1" outlineLevel="1">
+    <row r="13">
       <c r="B13" s="3" t="n"/>
       <c r="D13" s="4" t="n"/>
     </row>
-    <row r="14" hidden="1" outlineLevel="1">
+    <row r="14">
       <c r="B14" s="6" t="inlineStr">
         <is>
           <t>GENERATED</t>
@@ -2169,7 +2169,7 @@
       <c r="C14" s="11" t="n"/>
       <c r="D14" s="11" t="n"/>
     </row>
-    <row r="15" hidden="1" outlineLevel="1">
+    <row r="15">
       <c r="B15" s="16" t="inlineStr">
         <is>
           <t>Balance, June 1, 2026</t>
@@ -2220,7 +2220,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="20" collapsed="1">
+    <row r="20" hidden="1" outlineLevel="1">
       <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Parts used — Priya S.</t>
@@ -2231,7 +2231,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="21" outlineLevel="1">
+    <row r="21" hidden="1" outlineLevel="1">
       <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Repair collected — Liam O.</t>
@@ -2241,7 +2241,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="22" outlineLevel="1">
+    <row r="22" hidden="1" outlineLevel="1">
       <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Parts used — Liam O.</t>
@@ -2251,7 +2251,7 @@
         <v>-95</v>
       </c>
     </row>
-    <row r="23" outlineLevel="1">
+    <row r="23" hidden="1" outlineLevel="1">
       <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Repair collected — Sofia M.</t>
@@ -2261,7 +2261,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="24" outlineLevel="1">
+    <row r="24" hidden="1" outlineLevel="1">
       <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Repair collected — Jamal W.</t>
@@ -2271,7 +2271,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="25" outlineLevel="1">
+    <row r="25" hidden="1" outlineLevel="1">
       <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Parts used — Jamal W.</t>
@@ -2281,7 +2281,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="26" outlineLevel="1">
+    <row r="26" hidden="1" outlineLevel="1">
       <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Repair collected — Erin K.</t>
@@ -2291,7 +2291,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="27" outlineLevel="1">
+    <row r="27" hidden="1" outlineLevel="1">
       <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Parts used — Erin K.</t>
@@ -2301,7 +2301,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="28" outlineLevel="1">
+    <row r="28" hidden="1" outlineLevel="1">
       <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Repair collected — Noah B.</t>
@@ -2311,7 +2311,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="29" outlineLevel="1">
+    <row r="29" hidden="1" outlineLevel="1">
       <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Parts used — Noah B.</t>
@@ -2321,7 +2321,7 @@
         <v>-65</v>
       </c>
     </row>
-    <row r="30" outlineLevel="1">
+    <row r="30" hidden="1" outlineLevel="1">
       <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Rent used — June</t>
@@ -2331,7 +2331,7 @@
         <v>-650</v>
       </c>
     </row>
-    <row r="31" outlineLevel="1">
+    <row r="31" hidden="1" outlineLevel="1">
       <c r="B31" s="3" t="inlineStr">
         <is>
           <t>Rent used — July</t>
@@ -2341,7 +2341,7 @@
         <v>-650</v>
       </c>
     </row>
-    <row r="32" outlineLevel="1">
+    <row r="32" hidden="1" outlineLevel="1">
       <c r="B32" s="3" t="inlineStr">
         <is>
           <t>Repair collected — Grace L.</t>
@@ -2351,7 +2351,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="33" outlineLevel="1">
+    <row r="33" hidden="1" outlineLevel="1">
       <c r="B33" s="3" t="inlineStr">
         <is>
           <t>Parts used — Grace L.</t>
@@ -2361,7 +2361,7 @@
         <v>-35</v>
       </c>
     </row>
-    <row r="34" outlineLevel="1">
+    <row r="34" hidden="1" outlineLevel="1">
       <c r="B34" s="3" t="inlineStr">
         <is>
           <t>Repair collected — Theo H.</t>
@@ -2371,7 +2371,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="35" outlineLevel="1">
+    <row r="35" hidden="1" outlineLevel="1">
       <c r="B35" s="3" t="inlineStr">
         <is>
           <t>Parts used — Theo H.</t>
@@ -2381,7 +2381,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="36" outlineLevel="1">
+    <row r="36" hidden="1" outlineLevel="1">
       <c r="B36" s="3" t="inlineStr">
         <is>
           <t>Repair collected — Maya P.</t>
@@ -2391,7 +2391,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="37" outlineLevel="1">
+    <row r="37" hidden="1" outlineLevel="1">
       <c r="B37" s="3" t="inlineStr">
         <is>
           <t>Parts used — Maya P.</t>
@@ -2401,7 +2401,7 @@
         <v>-125</v>
       </c>
     </row>
-    <row r="38" outlineLevel="1">
+    <row r="38" hidden="1" outlineLevel="1">
       <c r="B38" s="3" t="inlineStr">
         <is>
           <t>Repair collected — Owen C.</t>
@@ -2411,7 +2411,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="39" outlineLevel="1">
+    <row r="39" hidden="1" outlineLevel="1">
       <c r="B39" s="3" t="inlineStr">
         <is>
           <t>Parts used — Owen C.</t>
@@ -2421,7 +2421,7 @@
         <v>-55</v>
       </c>
     </row>
-    <row r="40" outlineLevel="1">
+    <row r="40" hidden="1" outlineLevel="1">
       <c r="B40" s="3" t="inlineStr">
         <is>
           <t>Repair collected — Ava D.</t>
@@ -2431,7 +2431,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="41" outlineLevel="1">
+    <row r="41" hidden="1" outlineLevel="1">
       <c r="B41" s="3" t="inlineStr">
         <is>
           <t>Parts used — Ava D.</t>
@@ -2441,7 +2441,7 @@
         <v>-45</v>
       </c>
     </row>
-    <row r="42" outlineLevel="1">
+    <row r="42" hidden="1" outlineLevel="1">
       <c r="B42" s="3" t="inlineStr">
         <is>
           <t>Repair collected — Leo F.</t>
@@ -2451,7 +2451,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="43" outlineLevel="1">
+    <row r="43" hidden="1" outlineLevel="1">
       <c r="B43" s="3" t="inlineStr">
         <is>
           <t>Parts used — Leo F.</t>
@@ -2461,7 +2461,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="44" outlineLevel="1">
+    <row r="44" hidden="1" outlineLevel="1">
       <c r="B44" s="3" t="inlineStr">
         <is>
           <t>Repair collected — Nina V.</t>
@@ -2471,7 +2471,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="45" outlineLevel="1">
+    <row r="45" hidden="1" outlineLevel="1">
       <c r="B45" s="3" t="inlineStr">
         <is>
           <t>Parts used — Nina V.</t>
@@ -2481,7 +2481,7 @@
         <v>-80</v>
       </c>
     </row>
-    <row r="46" outlineLevel="1">
+    <row r="46" hidden="1" outlineLevel="1">
       <c r="B46" s="3" t="inlineStr">
         <is>
           <t>Rent used — August</t>
@@ -2491,7 +2491,7 @@
         <v>-650</v>
       </c>
     </row>
-    <row r="47" outlineLevel="1">
+    <row r="47" hidden="1" outlineLevel="1">
       <c r="B47" s="3" t="inlineStr">
         <is>
           <t>Repair collected — Caleb G.</t>
@@ -2501,7 +2501,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="48" outlineLevel="1">
+    <row r="48" hidden="1" outlineLevel="1">
       <c r="B48" s="3" t="inlineStr">
         <is>
           <t>Parts used — Caleb G.</t>
@@ -2511,7 +2511,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="49" outlineLevel="1">
+    <row r="49" hidden="1" outlineLevel="1">
       <c r="B49" s="3" t="inlineStr">
         <is>
           <t>Repair collected — Ruth A.</t>
@@ -2521,7 +2521,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="50" outlineLevel="1">
+    <row r="50" hidden="1" outlineLevel="1">
       <c r="B50" s="3" t="inlineStr">
         <is>
           <t>Parts used — Ruth A.</t>
@@ -2531,7 +2531,7 @@
         <v>-129</v>
       </c>
     </row>
-    <row r="51" outlineLevel="1">
+    <row r="51" hidden="1" outlineLevel="1">
       <c r="B51" s="3" t="inlineStr">
         <is>
           <t>Repair collected — Sam Q.</t>
@@ -2541,7 +2541,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="52" outlineLevel="1">
+    <row r="52" hidden="1" outlineLevel="1">
       <c r="B52" s="3" t="inlineStr">
         <is>
           <t>Parts used — Sam Q.</t>
@@ -2551,7 +2551,7 @@
         <v>-70</v>
       </c>
     </row>
-    <row r="53" outlineLevel="1">
+    <row r="53" hidden="1" outlineLevel="1">
       <c r="B53" s="3" t="inlineStr">
         <is>
           <t>Repair collected — Westville Bike Share</t>
@@ -2561,7 +2561,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="54" outlineLevel="1">
+    <row r="54" hidden="1" outlineLevel="1">
       <c r="B54" s="3" t="inlineStr">
         <is>
           <t>Parts used — Westville Bike Share</t>
@@ -2571,7 +2571,7 @@
         <v>-105</v>
       </c>
     </row>
-    <row r="55" outlineLevel="1">
+    <row r="55" hidden="1" outlineLevel="1">
       <c r="B55" s="3" t="inlineStr">
         <is>
           <t>Repair delivered — Ridgeline Trail Crew, billed net 15 (unpaid)</t>
@@ -2581,7 +2581,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="56" outlineLevel="1">
+    <row r="56" hidden="1" outlineLevel="1">
       <c r="B56" s="3" t="inlineStr">
         <is>
           <t>Parts used — Ridgeline Trail Crew</t>
@@ -2591,7 +2591,7 @@
         <v>-75</v>
       </c>
     </row>
-    <row r="57" outlineLevel="1">
+    <row r="57" hidden="1" outlineLevel="1">
       <c r="B57" s="3" t="inlineStr">
         <is>
           <t>Frame delivered — J. Smith (deposit earned)</t>
@@ -2601,7 +2601,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="58" outlineLevel="1">
+    <row r="58" hidden="1" outlineLevel="1">
       <c r="B58" s="3" t="inlineStr">
         <is>
           <t>Parts used — J. Smith</t>
@@ -2611,7 +2611,7 @@
         <v>-36</v>
       </c>
     </row>
-    <row r="59" outlineLevel="1">
+    <row r="59" hidden="1" outlineLevel="1">
       <c r="B59" s="3" t="inlineStr">
         <is>
           <t>Depreciation — tools &amp; repair equipment, Summer 2026</t>
@@ -2621,7 +2621,7 @@
         <v>-160</v>
       </c>
     </row>
-    <row r="60" outlineLevel="1">
+    <row r="60" hidden="1" outlineLevel="1">
       <c r="B60" s="3" t="inlineStr">
         <is>
           <t>Depreciation — fixtures, Summer 2026</t>
@@ -2631,7 +2631,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="61" outlineLevel="1">
+    <row r="61" hidden="1" outlineLevel="1">
       <c r="B61" s="3" t="inlineStr">
         <is>
           <t>Depreciation — laptop, Summer 2026</t>
@@ -2641,7 +2641,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="62" outlineLevel="1">
+    <row r="62" collapsed="1">
       <c r="B62" s="16" t="inlineStr">
         <is>
           <t>Balance, August 31, 2026</t>
@@ -2654,11 +2654,11 @@
         <v/>
       </c>
     </row>
-    <row r="63" outlineLevel="1">
+    <row r="63">
       <c r="B63" s="3" t="n"/>
       <c r="D63" s="4" t="n"/>
     </row>
-    <row r="64" outlineLevel="1">
+    <row r="64">
       <c r="B64" s="6" t="inlineStr">
         <is>
           <t>WITHDRAWN</t>
@@ -2667,7 +2667,7 @@
       <c r="C64" s="11" t="n"/>
       <c r="D64" s="11" t="n"/>
     </row>
-    <row r="65" outlineLevel="1">
+    <row r="65">
       <c r="B65" s="16" t="inlineStr">
         <is>
           <t>Balance, June 1, 2026</t>
@@ -2678,7 +2678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" outlineLevel="1">
+    <row r="66" hidden="1" outlineLevel="1">
       <c r="B66" s="3" t="inlineStr">
         <is>
           <t>Owner's draw — money taken out for personal use</t>
@@ -2688,7 +2688,7 @@
         <v>-600</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" collapsed="1">
       <c r="B67" s="16" t="inlineStr">
         <is>
           <t>Balance, August 31, 2026</t>

--- a/Bike-Repair-Source-Workbooks/Bike-Repair-Module-3-3.xlsx
+++ b/Bike-Repair-Source-Workbooks/Bike-Repair-Module-3-3.xlsx
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:D132"/>
+  <dimension ref="B1:D100"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -549,1275 +549,986 @@
       <c r="C2" s="11" t="n"/>
       <c r="D2" s="11" t="n"/>
     </row>
-    <row r="3" outlineLevel="1">
+    <row r="3" hidden="1" outlineLevel="1">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Rent paid in advance (the lease)</t>
+          <t>Company received at formation (June 1)</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>-1300</v>
-      </c>
-    </row>
-    <row r="4" outlineLevel="1">
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Park Tool repair stand</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>-200</v>
-      </c>
-    </row>
-    <row r="5" outlineLevel="1">
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Repair, customer paid</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="6" outlineLevel="1">
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Repair, customer paid</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="7" outlineLevel="1">
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Repair, customer paid</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" outlineLevel="1">
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Repair, customer paid</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="9" outlineLevel="1">
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Repair, customer paid</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="10" outlineLevel="1">
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Smith's deposit received</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="11" outlineLevel="1">
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Repair, customer paid</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" outlineLevel="1">
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Repair, customer paid</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="13" outlineLevel="1">
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Covered from your personal funds</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="14" outlineLevel="1">
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Deposited to open the LLC bank account</t>
-        </is>
-      </c>
-      <c r="D14" s="15" t="n">
         <v>1300</v>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="16" t="inlineStr">
+    <row r="4" collapsed="1">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>Balance, June 1, 2026</t>
         </is>
       </c>
-      <c r="C15" s="17" t="n"/>
-      <c r="D15" s="13">
-        <f>SUBTOTAL(9,D3:D14)</f>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="13">
+        <f>SUM(D3:D3)</f>
         <v>1300</v>
         <v/>
       </c>
     </row>
-    <row r="16" outlineLevel="1">
+    <row r="5" hidden="1" outlineLevel="1">
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Repair collected — Dana R.</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" hidden="1" outlineLevel="1">
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Repair collected — Marcus T.</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="7" hidden="1" outlineLevel="1">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Repair collected — Priya S.</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="8" hidden="1" outlineLevel="1">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Repair collected — Liam O.</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="9" hidden="1" outlineLevel="1">
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Repair collected — Sofia M.</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10" hidden="1" outlineLevel="1">
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Repair collected — Jamal W.</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="11" hidden="1" outlineLevel="1">
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Repair collected — Erin K.</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="12" hidden="1" outlineLevel="1">
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Repair collected — Noah B.</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="13" hidden="1" outlineLevel="1">
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Repair collected — Grace L.</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="14" hidden="1" outlineLevel="1">
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Repair collected — Theo H.</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="15" hidden="1" outlineLevel="1">
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Repair collected — Maya P.</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="4" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="16" hidden="1" outlineLevel="1">
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Dana R.</t>
+          <t>Repair collected — Owen C.</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="17" outlineLevel="1">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="17" hidden="1" outlineLevel="1">
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Marcus T.</t>
+          <t>Repair collected — Ava D.</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="18" outlineLevel="1">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="18" hidden="1" outlineLevel="1">
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Priya S.</t>
+          <t>Repair collected — Leo F.</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="19" outlineLevel="1">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="19" hidden="1" outlineLevel="1">
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Liam O.</t>
+          <t>Repair collected — Nina V.</t>
         </is>
       </c>
       <c r="D19" s="4" t="n">
         <v>300</v>
       </c>
     </row>
-    <row r="20" outlineLevel="1">
+    <row r="20" hidden="1" outlineLevel="1">
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Sofia M.</t>
+          <t>Repair collected — Caleb G.</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="21" outlineLevel="1">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="21" hidden="1" outlineLevel="1">
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Jamal W.</t>
+          <t>Repair collected — Ruth A.</t>
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="22" outlineLevel="1">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="22" hidden="1" outlineLevel="1">
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Erin K.</t>
+          <t>Repair collected — Sam Q.</t>
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="23" outlineLevel="1">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="23" hidden="1" outlineLevel="1">
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Noah B.</t>
+          <t>Repair collected — Westville Bike Share</t>
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="24" outlineLevel="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="24" hidden="1" outlineLevel="1">
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Grace L.</t>
+          <t>Parts bought — June</t>
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="25" outlineLevel="1">
+        <v>-500</v>
+      </c>
+    </row>
+    <row r="25" hidden="1" outlineLevel="1">
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Theo H.</t>
+          <t>Parts bought — July</t>
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="26" outlineLevel="1">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="26" hidden="1" outlineLevel="1">
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Maya P.</t>
+          <t>Parts bought — August</t>
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="27" outlineLevel="1">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="27" hidden="1" outlineLevel="1">
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Owen C.</t>
+          <t>Rent paid — June</t>
         </is>
       </c>
       <c r="D27" s="4" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="28" outlineLevel="1">
+        <v>-650</v>
+      </c>
+    </row>
+    <row r="28" hidden="1" outlineLevel="1">
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Ava D.</t>
+          <t>Rent paid — July</t>
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="29" outlineLevel="1">
+        <v>-650</v>
+      </c>
+    </row>
+    <row r="29" hidden="1" outlineLevel="1">
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Leo F.</t>
+          <t>Rent paid — August</t>
         </is>
       </c>
       <c r="D29" s="4" t="n">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="30" outlineLevel="1">
+        <v>-650</v>
+      </c>
+    </row>
+    <row r="30" hidden="1" outlineLevel="1">
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Nina V.</t>
+          <t>New repair tool</t>
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="31" outlineLevel="1">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="31" hidden="1" outlineLevel="1">
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Caleb G.</t>
+          <t>Credit card paid off</t>
         </is>
       </c>
       <c r="D31" s="4" t="n">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="32" outlineLevel="1">
+        <v>-2030</v>
+      </c>
+    </row>
+    <row r="32" hidden="1" outlineLevel="1">
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Ruth A.</t>
+          <t>Money taken out for personal use</t>
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="33" outlineLevel="1">
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>Repair collected — Sam Q.</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="34" outlineLevel="1">
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>Repair collected — Westville Bike Share</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="35" outlineLevel="1">
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>Parts bought — June</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>-500</v>
-      </c>
-    </row>
-    <row r="36" outlineLevel="1">
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>Parts bought — July</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="n">
-        <v>-400</v>
-      </c>
-    </row>
-    <row r="37" outlineLevel="1">
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>Parts bought — August</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>-300</v>
-      </c>
-    </row>
-    <row r="38" outlineLevel="1">
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>Rent paid — June</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="n">
-        <v>-650</v>
-      </c>
-    </row>
-    <row r="39" outlineLevel="1">
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>Rent paid — July</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>-650</v>
-      </c>
-    </row>
-    <row r="40" outlineLevel="1">
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>Rent paid — August</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="n">
-        <v>-650</v>
-      </c>
-    </row>
-    <row r="41" outlineLevel="1">
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>New repair tool</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="n">
-        <v>-400</v>
-      </c>
-    </row>
-    <row r="42" outlineLevel="1">
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>Credit card paid off</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="n">
-        <v>-2030</v>
-      </c>
-    </row>
-    <row r="43" outlineLevel="1">
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>Money taken out for personal use</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="n">
         <v>-600</v>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" s="16" t="inlineStr">
+    <row r="33" collapsed="1">
+      <c r="B33" s="16" t="inlineStr">
         <is>
           <t>Balance, August 31, 2026</t>
         </is>
       </c>
-      <c r="C44" s="17" t="n"/>
-      <c r="D44" s="13">
-        <f>SUBTOTAL(9,D3:D43)</f>
+      <c r="C33" s="17" t="n"/>
+      <c r="D33" s="13">
+        <f>D4+SUM(D5:D32)</f>
         <v>620</v>
         <v/>
       </c>
     </row>
-    <row r="46">
-      <c r="B46" s="6" t="inlineStr">
+    <row r="34">
+      <c r="B34" s="7" t="n"/>
+      <c r="D34" s="4" t="n"/>
+    </row>
+    <row r="35" hidden="1" outlineLevel="1">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="C46" s="11" t="n"/>
-      <c r="D46" s="11" t="n"/>
-    </row>
-    <row r="47" outlineLevel="1">
-      <c r="B47" s="3" t="inlineStr">
+      <c r="C35" s="11" t="n"/>
+      <c r="D35" s="11" t="n"/>
+    </row>
+    <row r="36" hidden="1" outlineLevel="1">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>Ridgeline Trail Crew — finished Aug 28, net 15 (unpaid)</t>
         </is>
       </c>
-      <c r="D47" s="4" t="n">
+      <c r="D36" s="4" t="n">
         <v>300</v>
       </c>
     </row>
-    <row r="48">
-      <c r="B48" s="16" t="inlineStr">
+    <row r="37" collapsed="1">
+      <c r="B37" s="16" t="inlineStr">
         <is>
           <t>Balance, August 31, 2026</t>
         </is>
       </c>
-      <c r="C48" s="17" t="n"/>
-      <c r="D48" s="13">
-        <f>SUBTOTAL(9,D47)</f>
+      <c r="C37" s="17" t="n"/>
+      <c r="D37" s="13">
+        <f>SUM(D36:D36)</f>
         <v>300</v>
         <v/>
       </c>
     </row>
-    <row r="50">
-      <c r="B50" s="6" t="inlineStr">
+    <row r="38">
+      <c r="B38" s="7" t="n"/>
+      <c r="D38" s="4" t="n"/>
+    </row>
+    <row r="39">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>Right of Use</t>
         </is>
       </c>
-      <c r="C50" s="11" t="n"/>
-      <c r="D50" s="11" t="n"/>
-    </row>
-    <row r="51" outlineLevel="1">
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>Last month's rent, paid in advance (on deposit)</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="n">
+      <c r="C39" s="11" t="n"/>
+      <c r="D39" s="11" t="n"/>
+    </row>
+    <row r="40" hidden="1" outlineLevel="1">
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Company received at formation (June 1)</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="n">
         <v>650</v>
       </c>
     </row>
-    <row r="52">
-      <c r="B52" s="16" t="inlineStr">
+    <row r="41" collapsed="1">
+      <c r="B41" s="16" t="inlineStr">
         <is>
           <t>Balance, June 1, 2026</t>
         </is>
       </c>
-      <c r="C52" s="17" t="n"/>
-      <c r="D52" s="13">
-        <f>D51</f>
+      <c r="C41" s="17" t="n"/>
+      <c r="D41" s="13">
+        <f>SUM(D40:D40)</f>
         <v>650</v>
         <v/>
       </c>
     </row>
-    <row r="53">
-      <c r="B53" s="16" t="inlineStr">
+    <row r="42">
+      <c r="B42" s="16" t="inlineStr">
         <is>
           <t>Balance, August 31, 2026</t>
         </is>
       </c>
-      <c r="C53" s="17" t="n"/>
-      <c r="D53" s="13">
-        <f>D51</f>
+      <c r="C42" s="17" t="n"/>
+      <c r="D42" s="13">
+        <f>D41</f>
         <v>650</v>
         <v/>
       </c>
     </row>
-    <row r="55">
-      <c r="B55" s="6" t="inlineStr">
+    <row r="43">
+      <c r="B43" s="7" t="n"/>
+      <c r="D43" s="4" t="n"/>
+    </row>
+    <row r="44">
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>Parts</t>
         </is>
       </c>
+      <c r="C44" s="11" t="n"/>
+      <c r="D44" s="11" t="n"/>
+    </row>
+    <row r="45" hidden="1" outlineLevel="1">
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Company received at formation (June 1)</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="46" collapsed="1">
+      <c r="B46" s="16" t="inlineStr">
+        <is>
+          <t>Balance, June 1, 2026</t>
+        </is>
+      </c>
+      <c r="C46" s="17" t="n"/>
+      <c r="D46" s="13">
+        <f>SUM(D45:D45)</f>
+        <v>200</v>
+        <v/>
+      </c>
+    </row>
+    <row r="47" hidden="1" outlineLevel="1">
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Chains ×10 (June)</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="48" hidden="1" outlineLevel="1">
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>11-spd cassettes ×4 (June)</t>
+        </is>
+      </c>
+      <c r="C48" s="17" t="n"/>
+      <c r="D48" s="4" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="49" hidden="1" outlineLevel="1">
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Brake pad sets ×12 (June)</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="50" hidden="1" outlineLevel="1">
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Cables + housing (assorted) (June)</t>
+        </is>
+      </c>
+      <c r="C50" s="11" t="n"/>
+      <c r="D50" s="4" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="51" hidden="1" outlineLevel="1">
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Tubes ×10 (June)</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="52" hidden="1" outlineLevel="1">
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Chainrings + jockey wheels (July)</t>
+        </is>
+      </c>
+      <c r="C52" s="17" t="n"/>
+      <c r="D52" s="4" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="53" hidden="1" outlineLevel="1">
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Bottom brackets ×3 (July)</t>
+        </is>
+      </c>
+      <c r="C53" s="17" t="n"/>
+      <c r="D53" s="4" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="54" hidden="1" outlineLevel="1">
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Shift cables + housing (July)</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="55" hidden="1" outlineLevel="1">
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Tubeless sealant + valves (July)</t>
+        </is>
+      </c>
       <c r="C55" s="11" t="n"/>
-      <c r="D55" s="11" t="n"/>
-    </row>
-    <row r="56" outlineLevel="1">
+      <c r="D55" s="4" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="56" hidden="1" outlineLevel="1">
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Chains</t>
+          <t>Spokes + nipples (July)</t>
         </is>
       </c>
       <c r="D56" s="4" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="57" hidden="1" outlineLevel="1">
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Tires ×4 (August)</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="58" hidden="1" outlineLevel="1">
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Brake pads (assorted) (August)</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="59" hidden="1" outlineLevel="1">
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>Cables + housing (August)</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="57" outlineLevel="1">
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>Brake pads</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="58" outlineLevel="1">
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>Derailleur cables</t>
-        </is>
-      </c>
-      <c r="D58" s="4" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="59" outlineLevel="1">
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>Cassettes</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="60" outlineLevel="1">
+    <row r="60" hidden="1" outlineLevel="1">
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Bottom brackets</t>
+          <t>Tubes ×8 (August)</t>
         </is>
       </c>
       <c r="D60" s="4" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="61" outlineLevel="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="61" hidden="1" outlineLevel="1">
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Spokes</t>
+          <t>Small parts (bolts, tape) (August)</t>
         </is>
       </c>
       <c r="D61" s="4" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="62" outlineLevel="1">
+    <row r="62" hidden="1" outlineLevel="1">
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Tubes</t>
+          <t>Parts used — Dana R.</t>
         </is>
       </c>
       <c r="D62" s="4" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="16" t="inlineStr">
-        <is>
-          <t>Balance, June 1, 2026</t>
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="63" hidden="1" outlineLevel="1">
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Priya S.</t>
         </is>
       </c>
       <c r="C63" s="17" t="n"/>
-      <c r="D63" s="13">
-        <f>SUBTOTAL(9,D56:D62)</f>
+      <c r="D63" s="4" t="n">
+        <v>-25</v>
+      </c>
+    </row>
+    <row r="64" hidden="1" outlineLevel="1">
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Liam O.</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="n">
+        <v>-95</v>
+      </c>
+    </row>
+    <row r="65" hidden="1" outlineLevel="1">
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Jamal W.</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="n">
+        <v>-60</v>
+      </c>
+    </row>
+    <row r="66" hidden="1" outlineLevel="1">
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Erin K.</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="n">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="67" hidden="1" outlineLevel="1">
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Noah B.</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="n">
+        <v>-65</v>
+      </c>
+    </row>
+    <row r="68" hidden="1" outlineLevel="1">
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Grace L.</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="n">
+        <v>-35</v>
+      </c>
+    </row>
+    <row r="69" hidden="1" outlineLevel="1">
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Theo H.</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="n">
+        <v>-25</v>
+      </c>
+    </row>
+    <row r="70" hidden="1" outlineLevel="1">
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Maya P.</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="n">
+        <v>-125</v>
+      </c>
+    </row>
+    <row r="71" hidden="1" outlineLevel="1">
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Owen C.</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="n">
+        <v>-55</v>
+      </c>
+    </row>
+    <row r="72" hidden="1" outlineLevel="1">
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Ava D.</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="n">
+        <v>-45</v>
+      </c>
+    </row>
+    <row r="73" hidden="1" outlineLevel="1">
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Leo F.</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="n">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="74" hidden="1" outlineLevel="1">
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Nina V.</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="n">
+        <v>-80</v>
+      </c>
+    </row>
+    <row r="75" hidden="1" outlineLevel="1">
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Caleb G.</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="n">
+        <v>-25</v>
+      </c>
+    </row>
+    <row r="76" hidden="1" outlineLevel="1">
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Ruth A.</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="n">
+        <v>-129</v>
+      </c>
+    </row>
+    <row r="77" hidden="1" outlineLevel="1">
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Sam Q.</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="n">
+        <v>-70</v>
+      </c>
+    </row>
+    <row r="78" hidden="1" outlineLevel="1">
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Westville Bike Share</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="n">
+        <v>-105</v>
+      </c>
+    </row>
+    <row r="79" hidden="1" outlineLevel="1">
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Ridgeline Trail Crew</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="n">
+        <v>-75</v>
+      </c>
+    </row>
+    <row r="80" hidden="1" outlineLevel="1">
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — J. Smith</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>-36</v>
+      </c>
+    </row>
+    <row r="81" collapsed="1">
+      <c r="B81" s="16" t="inlineStr">
+        <is>
+          <t>Balance, August 31, 2026</t>
+        </is>
+      </c>
+      <c r="C81" s="17" t="n"/>
+      <c r="D81" s="13">
+        <f>D46+SUM(D47:D80)</f>
         <v>200</v>
         <v/>
       </c>
     </row>
-    <row r="64" outlineLevel="1">
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>Chains ×10 (June)</t>
-        </is>
-      </c>
-      <c r="D64" s="4" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="65" outlineLevel="1">
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>11-spd cassettes ×4 (June)</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="n">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="66" outlineLevel="1">
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>Brake pad sets ×12 (June)</t>
-        </is>
-      </c>
-      <c r="D66" s="4" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="67" outlineLevel="1">
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>Cables + housing (assorted) (June)</t>
-        </is>
-      </c>
-      <c r="D67" s="4" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="68" outlineLevel="1">
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>Tubes ×10 (June)</t>
-        </is>
-      </c>
-      <c r="D68" s="4" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="69" outlineLevel="1">
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>Chainrings + jockey wheels (July)</t>
-        </is>
-      </c>
-      <c r="D69" s="4" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="70" outlineLevel="1">
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>Bottom brackets ×3 (July)</t>
-        </is>
-      </c>
-      <c r="D70" s="4" t="n">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="71" outlineLevel="1">
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>Shift cables + housing (July)</t>
-        </is>
-      </c>
-      <c r="D71" s="4" t="n">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="72" outlineLevel="1">
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>Tubeless sealant + valves (July)</t>
-        </is>
-      </c>
-      <c r="D72" s="4" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="73" outlineLevel="1">
-      <c r="B73" s="3" t="inlineStr">
-        <is>
-          <t>Spokes + nipples (July)</t>
-        </is>
-      </c>
-      <c r="D73" s="4" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="74" outlineLevel="1">
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>Tires ×4 (August)</t>
-        </is>
-      </c>
-      <c r="D74" s="4" t="n">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="75" outlineLevel="1">
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>Brake pads (assorted) (August)</t>
-        </is>
-      </c>
-      <c r="D75" s="4" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="76" outlineLevel="1">
-      <c r="B76" s="3" t="inlineStr">
-        <is>
-          <t>Cables + housing (August)</t>
-        </is>
-      </c>
-      <c r="D76" s="4" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="77" outlineLevel="1">
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t>Tubes ×8 (August)</t>
-        </is>
-      </c>
-      <c r="D77" s="4" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="78" outlineLevel="1">
-      <c r="B78" s="3" t="inlineStr">
-        <is>
-          <t>Small parts (bolts, tape) (August)</t>
-        </is>
-      </c>
-      <c r="D78" s="4" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="79" outlineLevel="1">
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Dana R.</t>
-        </is>
-      </c>
-      <c r="D79" s="4" t="n">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="80" outlineLevel="1">
-      <c r="B80" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Priya S.</t>
-        </is>
-      </c>
-      <c r="D80" s="4" t="n">
-        <v>-25</v>
-      </c>
-    </row>
-    <row r="81" outlineLevel="1">
-      <c r="B81" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Liam O.</t>
-        </is>
-      </c>
-      <c r="D81" s="4" t="n">
-        <v>-95</v>
-      </c>
-    </row>
-    <row r="82" outlineLevel="1">
-      <c r="B82" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Jamal W.</t>
-        </is>
-      </c>
-      <c r="D82" s="4" t="n">
-        <v>-60</v>
-      </c>
-    </row>
-    <row r="83" outlineLevel="1">
-      <c r="B83" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Erin K.</t>
-        </is>
-      </c>
-      <c r="D83" s="4" t="n">
+    <row r="82">
+      <c r="B82" s="3" t="n"/>
+      <c r="D82" s="4" t="n"/>
+    </row>
+    <row r="83">
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>Tools &amp; Repair Equipment</t>
+        </is>
+      </c>
+      <c r="C83" s="11" t="n"/>
+      <c r="D83" s="11" t="n"/>
+    </row>
+    <row r="84" hidden="1" outlineLevel="1">
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>Company received at formation (June 1)</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="85" collapsed="1">
+      <c r="B85" s="16" t="inlineStr">
+        <is>
+          <t>Balance, June 1, 2026</t>
+        </is>
+      </c>
+      <c r="C85" s="17" t="n"/>
+      <c r="D85" s="13">
+        <f>SUM(D84:D84)</f>
+        <v>1200</v>
+        <v/>
+      </c>
+    </row>
+    <row r="86" hidden="1" outlineLevel="1">
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>New repair tool bought this season</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="87" hidden="1" outlineLevel="1">
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>Depreciation — Summer 2026 (the season's share of the cost)</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="n">
+        <v>-160</v>
+      </c>
+    </row>
+    <row r="88" collapsed="1">
+      <c r="B88" s="16" t="inlineStr">
+        <is>
+          <t>Balance, August 31, 2026</t>
+        </is>
+      </c>
+      <c r="C88" s="17" t="n"/>
+      <c r="D88" s="13">
+        <f>D85+SUM(D86:D87)</f>
+        <v>1440</v>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="3" t="n"/>
+      <c r="D89" s="4" t="n"/>
+    </row>
+    <row r="90">
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>Fixtures</t>
+        </is>
+      </c>
+      <c r="C90" s="11" t="n"/>
+      <c r="D90" s="11" t="n"/>
+    </row>
+    <row r="91" hidden="1" outlineLevel="1">
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>Company received at formation (June 1)</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="n">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="92" collapsed="1">
+      <c r="B92" s="16" t="inlineStr">
+        <is>
+          <t>Balance, June 1, 2026</t>
+        </is>
+      </c>
+      <c r="C92" s="17" t="n"/>
+      <c r="D92" s="13">
+        <f>SUM(D91:D91)</f>
+        <v>750</v>
+        <v/>
+      </c>
+    </row>
+    <row r="93" hidden="1" outlineLevel="1">
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>Depreciation — Summer 2026 (the season's share of the cost)</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="n">
         <v>-40</v>
       </c>
     </row>
-    <row r="84" outlineLevel="1">
-      <c r="B84" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Noah B.</t>
-        </is>
-      </c>
-      <c r="D84" s="4" t="n">
-        <v>-65</v>
-      </c>
-    </row>
-    <row r="85" outlineLevel="1">
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Grace L.</t>
-        </is>
-      </c>
-      <c r="D85" s="4" t="n">
-        <v>-35</v>
-      </c>
-    </row>
-    <row r="86" outlineLevel="1">
-      <c r="B86" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Theo H.</t>
-        </is>
-      </c>
-      <c r="D86" s="4" t="n">
-        <v>-25</v>
-      </c>
-    </row>
-    <row r="87" outlineLevel="1">
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Maya P.</t>
-        </is>
-      </c>
-      <c r="D87" s="4" t="n">
-        <v>-125</v>
-      </c>
-    </row>
-    <row r="88" outlineLevel="1">
-      <c r="B88" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Owen C.</t>
-        </is>
-      </c>
-      <c r="D88" s="4" t="n">
-        <v>-55</v>
-      </c>
-    </row>
-    <row r="89" outlineLevel="1">
-      <c r="B89" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Ava D.</t>
-        </is>
-      </c>
-      <c r="D89" s="4" t="n">
-        <v>-45</v>
-      </c>
-    </row>
-    <row r="90" outlineLevel="1">
-      <c r="B90" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Leo F.</t>
-        </is>
-      </c>
-      <c r="D90" s="4" t="n">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="91" outlineLevel="1">
-      <c r="B91" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Nina V.</t>
-        </is>
-      </c>
-      <c r="D91" s="4" t="n">
-        <v>-80</v>
-      </c>
-    </row>
-    <row r="92" outlineLevel="1">
-      <c r="B92" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Caleb G.</t>
-        </is>
-      </c>
-      <c r="D92" s="4" t="n">
-        <v>-25</v>
-      </c>
-    </row>
-    <row r="93" outlineLevel="1">
-      <c r="B93" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Ruth A.</t>
-        </is>
-      </c>
-      <c r="D93" s="4" t="n">
-        <v>-129</v>
-      </c>
-    </row>
-    <row r="94" outlineLevel="1">
-      <c r="B94" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Sam Q.</t>
-        </is>
-      </c>
-      <c r="D94" s="4" t="n">
-        <v>-70</v>
-      </c>
-    </row>
-    <row r="95" outlineLevel="1">
-      <c r="B95" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Westville Bike Share</t>
-        </is>
-      </c>
-      <c r="D95" s="4" t="n">
-        <v>-105</v>
-      </c>
-    </row>
-    <row r="96" outlineLevel="1">
-      <c r="B96" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Ridgeline Trail Crew</t>
-        </is>
-      </c>
-      <c r="D96" s="4" t="n">
-        <v>-75</v>
-      </c>
-    </row>
-    <row r="97" outlineLevel="1">
+    <row r="94" collapsed="1">
+      <c r="B94" s="16" t="inlineStr">
+        <is>
+          <t>Balance, August 31, 2026</t>
+        </is>
+      </c>
+      <c r="C94" s="17" t="n"/>
+      <c r="D94" s="13">
+        <f>D92+SUM(D93:D93)</f>
+        <v>710</v>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" s="3" t="n"/>
+      <c r="D95" s="4" t="n"/>
+    </row>
+    <row r="96">
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+      <c r="C96" s="11" t="n"/>
+      <c r="D96" s="11" t="n"/>
+    </row>
+    <row r="97" hidden="1" outlineLevel="1">
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Parts used — J. Smith</t>
+          <t>Company received at formation (June 1)</t>
         </is>
       </c>
       <c r="D97" s="4" t="n">
-        <v>-36</v>
-      </c>
-    </row>
-    <row r="98">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="98" collapsed="1">
       <c r="B98" s="16" t="inlineStr">
         <is>
-          <t>Balance, August 31, 2026</t>
+          <t>Balance, June 1, 2026</t>
         </is>
       </c>
       <c r="C98" s="17" t="n"/>
       <c r="D98" s="13">
-        <f>SUBTOTAL(9,D56:D97)</f>
-        <v>200</v>
-        <v/>
-      </c>
-    </row>
-    <row r="100">
-      <c r="B100" s="6" t="inlineStr">
-        <is>
-          <t>Tools &amp; Repair Equipment</t>
-        </is>
-      </c>
-      <c r="C100" s="11" t="n"/>
-      <c r="D100" s="11" t="n"/>
-    </row>
-    <row r="101" outlineLevel="1">
-      <c r="B101" s="3" t="inlineStr">
-        <is>
-          <t>Repair stand</t>
-        </is>
-      </c>
-      <c r="D101" s="4" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="102" outlineLevel="1">
-      <c r="B102" s="3" t="inlineStr">
-        <is>
-          <t>Air compressor</t>
-        </is>
-      </c>
-      <c r="D102" s="4" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="103" outlineLevel="1">
-      <c r="B103" s="3" t="inlineStr">
-        <is>
-          <t>Parts washer</t>
-        </is>
-      </c>
-      <c r="D103" s="4" t="n">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="104" outlineLevel="1">
-      <c r="B104" s="3" t="inlineStr">
-        <is>
-          <t>Wheel-truing stand</t>
-        </is>
-      </c>
-      <c r="D104" s="4" t="n">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="105" outlineLevel="1">
-      <c r="B105" s="3" t="inlineStr">
-        <is>
-          <t>Cone wrench set</t>
-        </is>
-      </c>
-      <c r="D105" s="4" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="106" outlineLevel="1">
-      <c r="B106" s="3" t="inlineStr">
-        <is>
-          <t>Torque wrench</t>
-        </is>
-      </c>
-      <c r="D106" s="4" t="n">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="107" outlineLevel="1">
-      <c r="B107" s="3" t="inlineStr">
-        <is>
-          <t>Hex/Allen set</t>
-        </is>
-      </c>
-      <c r="D107" s="4" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="108" outlineLevel="1">
-      <c r="B108" s="3" t="inlineStr">
-        <is>
-          <t>Cable cutters</t>
-        </is>
-      </c>
-      <c r="D108" s="4" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="109" outlineLevel="1">
-      <c r="B109" s="3" t="inlineStr">
-        <is>
-          <t>Chain breaker</t>
-        </is>
-      </c>
-      <c r="D109" s="4" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="110" outlineLevel="1">
-      <c r="B110" s="3" t="inlineStr">
-        <is>
-          <t>Tire levers</t>
-        </is>
-      </c>
-      <c r="D110" s="4" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="111" outlineLevel="1">
-      <c r="B111" s="3" t="inlineStr">
-        <is>
-          <t>Bench grinder</t>
-        </is>
-      </c>
-      <c r="D111" s="4" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="112" outlineLevel="1">
-      <c r="B112" s="3" t="inlineStr">
-        <is>
-          <t>Headset press</t>
-        </is>
-      </c>
-      <c r="D112" s="4" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="113" outlineLevel="1">
-      <c r="B113" s="3" t="inlineStr">
-        <is>
-          <t>Shop vacuum</t>
-        </is>
-      </c>
-      <c r="D113" s="4" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="B114" s="16" t="inlineStr">
-        <is>
-          <t>Balance, June 1, 2026</t>
-        </is>
-      </c>
-      <c r="C114" s="17" t="n"/>
-      <c r="D114" s="13">
-        <f>SUBTOTAL(9,D101:D113)</f>
-        <v>1200</v>
-        <v/>
-      </c>
-    </row>
-    <row r="115" outlineLevel="1">
-      <c r="B115" s="3" t="inlineStr">
-        <is>
-          <t>New repair tool bought this season</t>
-        </is>
-      </c>
-      <c r="D115" s="4" t="n">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="116" outlineLevel="1">
-      <c r="B116" s="3" t="inlineStr">
-        <is>
-          <t>Depreciation — Summer 2026 (the season's share of the cost)</t>
-        </is>
-      </c>
-      <c r="D116" s="4" t="n">
-        <v>-160</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="B117" s="16" t="inlineStr">
-        <is>
-          <t>Balance, August 31, 2026</t>
-        </is>
-      </c>
-      <c r="C117" s="17" t="n"/>
-      <c r="D117" s="13">
-        <f>SUBTOTAL(9,D101:D116)</f>
-        <v>1440</v>
-        <v/>
-      </c>
-    </row>
-    <row r="119">
-      <c r="B119" s="6" t="inlineStr">
-        <is>
-          <t>Fixtures</t>
-        </is>
-      </c>
-      <c r="C119" s="11" t="n"/>
-      <c r="D119" s="11" t="n"/>
-    </row>
-    <row r="120" outlineLevel="1">
-      <c r="B120" s="3" t="inlineStr">
-        <is>
-          <t>Desk</t>
-        </is>
-      </c>
-      <c r="D120" s="4" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="121" outlineLevel="1">
-      <c r="B121" s="3" t="inlineStr">
-        <is>
-          <t>Shelving units</t>
-        </is>
-      </c>
-      <c r="D121" s="4" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="122" outlineLevel="1">
-      <c r="B122" s="3" t="inlineStr">
-        <is>
-          <t>Display rack</t>
-        </is>
-      </c>
-      <c r="D122" s="4" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="123" outlineLevel="1">
-      <c r="B123" s="3" t="inlineStr">
-        <is>
-          <t>Pegboard + hooks</t>
-        </is>
-      </c>
-      <c r="D123" s="4" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="B124" s="16" t="inlineStr">
-        <is>
-          <t>Balance, June 1, 2026</t>
-        </is>
-      </c>
-      <c r="C124" s="17" t="n"/>
-      <c r="D124" s="13">
-        <f>SUBTOTAL(9,D120:D123)</f>
-        <v>750</v>
-        <v/>
-      </c>
-    </row>
-    <row r="125">
-      <c r="B125" s="3" t="inlineStr">
-        <is>
-          <t>Depreciation — Summer 2026 (the season's share of the cost)</t>
-        </is>
-      </c>
-      <c r="D125" s="4" t="n">
-        <v>-40</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="B126" s="16" t="inlineStr">
-        <is>
-          <t>Balance, August 31, 2026</t>
-        </is>
-      </c>
-      <c r="C126" s="17" t="n"/>
-      <c r="D126" s="13">
-        <f>SUBTOTAL(9,D120:D125)</f>
-        <v>710</v>
-        <v/>
-      </c>
-    </row>
-    <row r="128">
-      <c r="B128" s="6" t="inlineStr">
-        <is>
-          <t>Laptop</t>
-        </is>
-      </c>
-      <c r="C128" s="11" t="n"/>
-      <c r="D128" s="11" t="n"/>
-    </row>
-    <row r="129" outlineLevel="1">
-      <c r="B129" s="3" t="inlineStr">
-        <is>
-          <t>Laptop (from home)</t>
-        </is>
-      </c>
-      <c r="D129" s="4" t="n">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="B130" s="16" t="inlineStr">
-        <is>
-          <t>Balance, June 1, 2026</t>
-        </is>
-      </c>
-      <c r="C130" s="17" t="n"/>
-      <c r="D130" s="13">
-        <f>SUBTOTAL(9,D129)</f>
+        <f>SUM(D97:D97)</f>
         <v>610</v>
         <v/>
       </c>
     </row>
-    <row r="131" outlineLevel="1">
-      <c r="B131" s="3" t="inlineStr">
+    <row r="99" hidden="1" outlineLevel="1">
+      <c r="B99" s="3" t="inlineStr">
         <is>
           <t>Depreciation — Summer 2026 (the season's share of the cost)</t>
         </is>
       </c>
-      <c r="D131" s="4" t="n">
+      <c r="D99" s="4" t="n">
         <v>-30</v>
       </c>
     </row>
-    <row r="132">
-      <c r="B132" s="16" t="inlineStr">
+    <row r="100" collapsed="1">
+      <c r="B100" s="16" t="inlineStr">
         <is>
           <t>Balance, August 31, 2026</t>
         </is>
       </c>
-      <c r="C132" s="17" t="n"/>
-      <c r="D132" s="13">
-        <f>SUBTOTAL(9,D129:D131)</f>
+      <c r="C100" s="17" t="n"/>
+      <c r="D100" s="13">
+        <f>D98+SUM(D99:D99)</f>
         <v>580</v>
         <v/>
       </c>
@@ -1834,7 +1545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:D17"/>
+  <dimension ref="B1:D12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1862,150 +1573,106 @@
     <row r="3" hidden="1" outlineLevel="1">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Charged — hand tools</t>
+          <t>Company assumed the claim at formation (June 1)</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="4" hidden="1" outlineLevel="1">
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Charged — air compressor</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>180</v>
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="4" collapsed="1">
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>Balance, June 1, 2026</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="13">
+        <f>SUM(D3:D3)</f>
+        <v>2030</v>
+        <v/>
       </c>
     </row>
     <row r="5" hidden="1" outlineLevel="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Charged — parts washer</t>
+          <t>Paid off in full this season</t>
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="6" hidden="1" outlineLevel="1">
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Charged — wheel-truing stand</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="7" hidden="1" outlineLevel="1">
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Charged — fixtures</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="8" hidden="1" outlineLevel="1">
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Charged — parts (QBP order)</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="9" collapsed="1">
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>Balance, June 1, 2026</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="n"/>
-      <c r="D9" s="13">
-        <f>SUM(D3:D8)</f>
-        <v>2030</v>
-        <v/>
-      </c>
-    </row>
-    <row r="10" hidden="1" outlineLevel="1">
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Paid off in full this season</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n">
         <v>-2030</v>
       </c>
     </row>
-    <row r="11" collapsed="1">
-      <c r="B11" s="16" t="inlineStr">
+    <row r="6" collapsed="1">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>Balance, August 31, 2026</t>
         </is>
       </c>
-      <c r="C11" s="17" t="n"/>
-      <c r="D11" s="13">
-        <f>SUM(D9:D10)</f>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="13">
+        <f>D4+SUM(D5:D5)</f>
         <v>0</v>
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="6" t="inlineStr">
+    <row r="7">
+      <c r="B7" s="3" t="n"/>
+      <c r="D7" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Customer Deposit</t>
         </is>
       </c>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="11" t="n"/>
-    </row>
-    <row r="14" hidden="1" outlineLevel="1">
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Smith's advance for a custom frame</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="n">
+      <c r="C8" s="11" t="n"/>
+      <c r="D8" s="11" t="n"/>
+    </row>
+    <row r="9" hidden="1" outlineLevel="1">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Company assumed the claim at formation (June 1)</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="4" t="n">
         <v>220</v>
       </c>
     </row>
-    <row r="15" collapsed="1">
-      <c r="B15" s="16" t="inlineStr">
+    <row r="10" collapsed="1">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>Balance, June 1, 2026</t>
         </is>
       </c>
-      <c r="C15" s="17" t="n"/>
-      <c r="D15" s="13">
-        <f>SUM(D14)</f>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="13">
+        <f>SUM(D9:D9)</f>
         <v>220</v>
         <v/>
       </c>
     </row>
-    <row r="16" hidden="1" outlineLevel="1">
-      <c r="B16" s="3" t="inlineStr">
+    <row r="11" hidden="1" outlineLevel="1">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Built and delivered Smith's frame — no longer owed</t>
         </is>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="C11" s="17" t="n"/>
+      <c r="D11" s="4" t="n">
         <v>-220</v>
       </c>
     </row>
-    <row r="17" collapsed="1">
-      <c r="B17" s="16" t="inlineStr">
+    <row r="12" collapsed="1">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>Balance, August 31, 2026</t>
         </is>
       </c>
-      <c r="C17" s="17" t="n"/>
-      <c r="D17" s="13">
-        <f>SUM(D15:D16)</f>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="13">
+        <f>D10+SUM(D11:D11)</f>
         <v>0</v>
         <v/>
       </c>

--- a/Bike-Repair-Source-Workbooks/Bike-Repair-Module-3-3.xlsx
+++ b/Bike-Repair-Source-Workbooks/Bike-Repair-Module-3-3.xlsx
@@ -870,7 +870,7 @@
       <c r="B34" s="7" t="n"/>
       <c r="D34" s="4" t="n"/>
     </row>
-    <row r="35" hidden="1" outlineLevel="1">
+    <row r="35">
       <c r="B35" s="6" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
@@ -879,7 +879,7 @@
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="11" t="n"/>
     </row>
-    <row r="36" hidden="1" outlineLevel="1">
+    <row r="36" outlineLevel="1">
       <c r="B36" s="3" t="inlineStr">
         <is>
           <t>Ridgeline Trail Crew — finished Aug 28, net 15 (unpaid)</t>
@@ -889,7 +889,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="37" collapsed="1">
+    <row r="37">
       <c r="B37" s="16" t="inlineStr">
         <is>
           <t>Balance, August 31, 2026</t>

--- a/Bike-Repair-Source-Workbooks/Bike-Repair-Module-3-3.xlsx
+++ b/Bike-Repair-Source-Workbooks/Bike-Repair-Module-3-3.xlsx
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:D100"/>
+  <dimension ref="A1:D100"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
     <row r="3" hidden="1" outlineLevel="1">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Company received at formation (June 1)</t>
+          <t>additional contribution (Section 10)</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
@@ -569,7 +569,6 @@
       <c r="D4" s="13">
         <f>SUM(D3:D3)</f>
         <v>1300</v>
-        <v/>
       </c>
     </row>
     <row r="5" hidden="1" outlineLevel="1">
@@ -826,7 +825,7 @@
     <row r="30" hidden="1" outlineLevel="1">
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>New repair tool</t>
+          <t>Wheel truing stand</t>
         </is>
       </c>
       <c r="D30" s="4" t="n">
@@ -863,7 +862,6 @@
       <c r="D33" s="13">
         <f>D4+SUM(D5:D32)</f>
         <v>620</v>
-        <v/>
       </c>
     </row>
     <row r="34">
@@ -899,7 +897,6 @@
       <c r="D37" s="13">
         <f>SUM(D36:D36)</f>
         <v>300</v>
-        <v/>
       </c>
     </row>
     <row r="38">
@@ -935,7 +932,6 @@
       <c r="D41" s="13">
         <f>SUM(D40:D40)</f>
         <v>650</v>
-        <v/>
       </c>
     </row>
     <row r="42">
@@ -948,7 +944,6 @@
       <c r="D42" s="13">
         <f>D41</f>
         <v>650</v>
-        <v/>
       </c>
     </row>
     <row r="43">
@@ -984,7 +979,6 @@
       <c r="D46" s="13">
         <f>SUM(D45:D45)</f>
         <v>200</v>
-        <v/>
       </c>
     </row>
     <row r="47" hidden="1" outlineLevel="1">
@@ -1343,7 +1337,6 @@
       <c r="D81" s="13">
         <f>D46+SUM(D47:D80)</f>
         <v>200</v>
-        <v/>
       </c>
     </row>
     <row r="82">
@@ -1379,13 +1372,12 @@
       <c r="D85" s="13">
         <f>SUM(D84:D84)</f>
         <v>1200</v>
-        <v/>
       </c>
     </row>
     <row r="86" hidden="1" outlineLevel="1">
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>New repair tool bought this season</t>
+          <t>Wheel truing stand bought this season</t>
         </is>
       </c>
       <c r="D86" s="4" t="n">
@@ -1412,7 +1404,6 @@
       <c r="D88" s="13">
         <f>D85+SUM(D86:D87)</f>
         <v>1440</v>
-        <v/>
       </c>
     </row>
     <row r="89">
@@ -1448,7 +1439,6 @@
       <c r="D92" s="13">
         <f>SUM(D91:D91)</f>
         <v>750</v>
-        <v/>
       </c>
     </row>
     <row r="93" hidden="1" outlineLevel="1">
@@ -1471,7 +1461,6 @@
       <c r="D94" s="13">
         <f>D92+SUM(D93:D93)</f>
         <v>710</v>
-        <v/>
       </c>
     </row>
     <row r="95">
@@ -1507,7 +1496,6 @@
       <c r="D98" s="13">
         <f>SUM(D97:D97)</f>
         <v>610</v>
-        <v/>
       </c>
     </row>
     <row r="99" hidden="1" outlineLevel="1">
@@ -1530,7 +1518,6 @@
       <c r="D100" s="13">
         <f>D98+SUM(D99:D99)</f>
         <v>580</v>
-        <v/>
       </c>
     </row>
   </sheetData>
@@ -1545,7 +1532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:D12"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1590,7 +1577,6 @@
       <c r="D4" s="13">
         <f>SUM(D3:D3)</f>
         <v>2030</v>
-        <v/>
       </c>
     </row>
     <row r="5" hidden="1" outlineLevel="1">
@@ -1613,7 +1599,6 @@
       <c r="D6" s="13">
         <f>D4+SUM(D5:D5)</f>
         <v>0</v>
-        <v/>
       </c>
     </row>
     <row r="7">
@@ -1650,7 +1635,6 @@
       <c r="D10" s="13">
         <f>SUM(D9:D9)</f>
         <v>220</v>
-        <v/>
       </c>
     </row>
     <row r="11" hidden="1" outlineLevel="1">
@@ -1674,7 +1658,6 @@
       <c r="D12" s="13">
         <f>D10+SUM(D11:D11)</f>
         <v>0</v>
-        <v/>
       </c>
     </row>
   </sheetData>
@@ -1689,7 +1672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:D67"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1717,7 +1700,7 @@
     <row r="3" hidden="1" outlineLevel="1">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Cash — Company received at formation (June 1)</t>
+          <t>Cash — additional contribution (Section 10)</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
@@ -1807,7 +1790,6 @@
       <c r="D11" s="13">
         <f>SUM(D3:D10)</f>
         <v>2460</v>
-        <v/>
       </c>
     </row>
     <row r="12">
@@ -1820,7 +1802,6 @@
       <c r="D12" s="13">
         <f>D11</f>
         <v>2460</v>
-        <v/>
       </c>
     </row>
     <row r="13">
@@ -2318,7 +2299,6 @@
       <c r="D62" s="13">
         <f>SUBTOTAL(9,D16:D61)</f>
         <v>2640</v>
-        <v/>
       </c>
     </row>
     <row r="63">
@@ -2365,7 +2345,6 @@
       <c r="D67" s="13">
         <f>SUM(D65:D66)</f>
         <v>-600</v>
-        <v/>
       </c>
     </row>
     <row r="71" hidden="1" outlineLevel="1"/>
@@ -2382,7 +2361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:C19"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2572,7 +2551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:D50"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="5.5" customWidth="1" min="1" max="1"/>
